--- a/projecao_produtos_2026-03-10.xlsx
+++ b/projecao_produtos_2026-03-10.xlsx
@@ -50,11 +50,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00B91C1C"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -102,14 +102,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0FDF4"/>
-        <bgColor rgb="00F0FDF4"/>
+        <fgColor rgb="00FECACA"/>
+        <bgColor rgb="00FECACA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FECACA"/>
-        <bgColor rgb="00FECACA"/>
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,14 +177,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -577,7 +577,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Projeção de Estoque por Produto — Gerado em 10/03/2026 16:08</t>
+          <t>Projeção de Estoque por Produto — Gerado em 10/03/2026 16:37</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  03</t>
+          <t>ARARA RIO 08/22  |  Cód: 13.46.0060  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: M4  |  04</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -665,40 +665,40 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -711,34 +711,34 @@
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="6" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -750,129 +750,127 @@
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>86 dias</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>65 dias</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>35 dias</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>4 dias</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
+      <c r="C6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="9" t="inlineStr"/>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr"/>
-      <c r="J7" s="9" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
-      <c r="N7" s="9" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr"/>
+      <c r="L7" s="10" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
-      <c r="J8" s="9" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
-      <c r="N8" s="9" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>80 dias</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr"/>
+      <c r="L8" s="10" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ENCANTO CARIOCA 02/25  |  Cód: 13.46.0343  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  03</t>
+          <t>BRASIL ANIMAL PRINT 22  |  Cód: 13.46.0067  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: M6  |  C6</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -881,40 +879,40 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -927,34 +925,34 @@
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="6" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -966,131 +964,151 @@
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>333 dias</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>312 dias</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>282 dias</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>251 dias</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>221 dias</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>190 dias</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>159 dias</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>129 dias</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>98 dias</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>68 dias</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
+      <c r="C13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr"/>
+      <c r="D14" s="10" t="inlineStr"/>
       <c r="E14" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="F14" s="9" t="inlineStr"/>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr"/>
-      <c r="J14" s="9" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr"/>
-      <c r="N14" s="9" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr"/>
+      <c r="L14" s="10" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>120 dias</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
-      <c r="N15" s="9" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>310 dias</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>PASSAPORTES DA ALEGRIA 02/25  |  Cód: 13.46.0347  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  03</t>
+          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  03</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1099,40 +1117,40 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1145,34 +1163,34 @@
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1184,131 +1202,113 @@
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>16 dias</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="9" t="n">
+      <c r="C20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr"/>
-      <c r="D21" s="9" t="inlineStr"/>
+      <c r="C21" s="10" t="inlineStr"/>
+      <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr"/>
-      <c r="J21" s="9" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr"/>
-      <c r="L21" s="9" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr"/>
-      <c r="N21" s="9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>45 dias</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr"/>
-      <c r="J22" s="9" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="9" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr"/>
-      <c r="N22" s="9" t="inlineStr"/>
+      <c r="C22" s="10" t="inlineStr"/>
+      <c r="D22" s="10" t="inlineStr"/>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>ENCANTO TROPICAL 03/25  |  Cód: 13.46.0371  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  03</t>
+          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  06</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1317,40 +1317,40 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -1363,34 +1363,34 @@
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="5" t="inlineStr"/>
       <c r="E25" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1402,131 +1402,127 @@
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>91 dias</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>70 dias</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>40 dias</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>9 dias</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0</v>
+      <c r="C27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr"/>
-      <c r="D28" s="9" t="inlineStr"/>
+      <c r="C28" s="10" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr"/>
       <c r="E28" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="F28" s="9" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
-      <c r="I28" s="9" t="inlineStr"/>
-      <c r="J28" s="9" t="inlineStr"/>
-      <c r="K28" s="9" t="inlineStr"/>
-      <c r="L28" s="9" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr"/>
-      <c r="N28" s="9" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="10" t="inlineStr"/>
+      <c r="H28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr"/>
-      <c r="D29" s="9" t="inlineStr"/>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>77 dias</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr"/>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="9" t="inlineStr"/>
-      <c r="I29" s="9" t="inlineStr"/>
-      <c r="J29" s="9" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="9" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr"/>
-      <c r="N29" s="9" t="inlineStr"/>
+      <c r="C29" s="10" t="inlineStr"/>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>220 dias</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="10" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr"/>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ARARA RIO 08/22  |  Cód: 13.46.0060  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: M4  |  04</t>
+          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  18</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1535,40 +1531,40 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1581,34 +1577,34 @@
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="6" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33">
@@ -1620,131 +1616,149 @@
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>0</v>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>399 dias</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>378 dias</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>348 dias</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>317 dias</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>287 dias</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>256 dias</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>225 dias</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>195 dias</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>164 dias</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>134 dias</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9" t="n">
+      <c r="C34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr"/>
+      <c r="C35" s="10" t="inlineStr"/>
+      <c r="D35" s="10" t="inlineStr"/>
       <c r="E35" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="F35" s="9" t="inlineStr"/>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr"/>
-      <c r="I35" s="9" t="inlineStr"/>
-      <c r="J35" s="9" t="inlineStr"/>
-      <c r="K35" s="9" t="inlineStr"/>
-      <c r="L35" s="9" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr"/>
-      <c r="N35" s="9" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" s="10" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>80 dias</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr"/>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
-      <c r="J36" s="9" t="inlineStr"/>
-      <c r="K36" s="9" t="inlineStr"/>
-      <c r="L36" s="9" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr"/>
-      <c r="N36" s="9" t="inlineStr"/>
+      <c r="C36" s="10" t="inlineStr"/>
+      <c r="D36" s="10" t="inlineStr"/>
+      <c r="E36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="10" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  06</t>
+          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  42</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -1753,40 +1767,40 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1799,34 +1813,34 @@
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="5" t="inlineStr"/>
       <c r="E39" s="6" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1838,131 +1852,115 @@
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
+      <c r="C41" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr"/>
-      <c r="D42" s="9" t="inlineStr"/>
+      <c r="C42" s="10" t="inlineStr"/>
+      <c r="D42" s="10" t="inlineStr"/>
       <c r="E42" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="F42" s="9" t="inlineStr"/>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-      <c r="I42" s="9" t="inlineStr"/>
-      <c r="J42" s="9" t="inlineStr"/>
-      <c r="K42" s="9" t="inlineStr"/>
-      <c r="L42" s="9" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr"/>
-      <c r="N42" s="9" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" s="10" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr"/>
+      <c r="L42" s="10" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>220 dias</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr"/>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
-      <c r="I43" s="9" t="inlineStr"/>
-      <c r="J43" s="9" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
-      <c r="N43" s="9" t="inlineStr"/>
+      <c r="C43" s="10" t="inlineStr"/>
+      <c r="D43" s="10" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>25 dias</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr"/>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" s="10" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PAVAO 07/23  |  Cód: 13.46.0168  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: P3  |  10</t>
+          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  47</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -1971,40 +1969,40 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -2017,34 +2015,34 @@
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr"/>
       <c r="E46" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2056,129 +2054,137 @@
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>182 dias</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>161 dias</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>131 dias</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>100 dias</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>70 dias</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>39 dias</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>8 dias</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>0</v>
+      <c r="C48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="9" t="n">
+      <c r="F48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr"/>
-      <c r="D49" s="9" t="inlineStr"/>
+      <c r="C49" s="10" t="inlineStr"/>
+      <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F49" s="9" t="inlineStr"/>
-      <c r="G49" s="9" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr"/>
-      <c r="I49" s="9" t="inlineStr"/>
-      <c r="J49" s="9" t="inlineStr"/>
-      <c r="K49" s="9" t="inlineStr"/>
-      <c r="L49" s="9" t="inlineStr"/>
-      <c r="M49" s="9" t="inlineStr"/>
-      <c r="N49" s="9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr"/>
+      <c r="G49" s="10" t="inlineStr"/>
+      <c r="H49" s="10" t="inlineStr"/>
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="inlineStr"/>
+      <c r="L49" s="10" t="inlineStr"/>
+      <c r="M49" s="10" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr"/>
-      <c r="D50" s="9" t="inlineStr"/>
+      <c r="C50" s="10" t="inlineStr"/>
+      <c r="D50" s="10" t="inlineStr"/>
       <c r="E50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="9" t="inlineStr"/>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr"/>
-      <c r="K50" s="9" t="inlineStr"/>
-      <c r="L50" s="9" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="9" t="inlineStr"/>
+      <c r="F50" s="10" t="inlineStr"/>
+      <c r="G50" s="10" t="inlineStr"/>
+      <c r="H50" s="10" t="inlineStr"/>
+      <c r="I50" s="10" t="inlineStr"/>
+      <c r="J50" s="10" t="inlineStr"/>
+      <c r="K50" s="10" t="inlineStr"/>
+      <c r="L50" s="10" t="inlineStr"/>
+      <c r="M50" s="10" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>ARARA AZUL 07/23  |  Cód: 13.46.0176  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: P3  |  10</t>
+          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  U9</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -2187,40 +2193,40 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
@@ -2233,34 +2239,34 @@
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="5" t="inlineStr"/>
       <c r="E53" s="6" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -2272,129 +2278,151 @@
       </c>
       <c r="C54" s="5" t="inlineStr"/>
       <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>302 dias</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>281 dias</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>251 dias</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>220 dias</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>190 dias</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>159 dias</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>128 dias</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>98 dias</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>67 dias</t>
+        </is>
+      </c>
+      <c r="N54" s="8" t="inlineStr">
+        <is>
+          <t>37 dias</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="9" t="n">
-        <v>0</v>
+      <c r="C55" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr"/>
-      <c r="D56" s="9" t="inlineStr"/>
+      <c r="C56" s="10" t="inlineStr"/>
+      <c r="D56" s="10" t="inlineStr"/>
       <c r="E56" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="F56" s="9" t="inlineStr"/>
-      <c r="G56" s="9" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
-      <c r="I56" s="9" t="inlineStr"/>
-      <c r="J56" s="9" t="inlineStr"/>
-      <c r="K56" s="9" t="inlineStr"/>
-      <c r="L56" s="9" t="inlineStr"/>
-      <c r="M56" s="9" t="inlineStr"/>
-      <c r="N56" s="9" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="F56" s="10" t="inlineStr"/>
+      <c r="G56" s="10" t="inlineStr"/>
+      <c r="H56" s="10" t="inlineStr"/>
+      <c r="I56" s="10" t="inlineStr"/>
+      <c r="J56" s="10" t="inlineStr"/>
+      <c r="K56" s="10" t="inlineStr"/>
+      <c r="L56" s="10" t="inlineStr"/>
+      <c r="M56" s="10" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
-      <c r="E57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="9" t="inlineStr"/>
-      <c r="G57" s="9" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr"/>
-      <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
-      <c r="K57" s="9" t="inlineStr"/>
-      <c r="L57" s="9" t="inlineStr"/>
-      <c r="M57" s="9" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr"/>
+      <c r="C57" s="10" t="inlineStr"/>
+      <c r="D57" s="10" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>660 dias</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr"/>
+      <c r="G57" s="10" t="inlineStr"/>
+      <c r="H57" s="10" t="inlineStr"/>
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>TIJUCA 08/23  |  Cód: 13.46.0177  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: Q1  |  10</t>
+          <t>PAVAO 07/23  |  Cód: 13.46.0168  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: P3  |  10</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -2403,40 +2431,40 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -2449,34 +2477,34 @@
       <c r="C60" s="5" t="inlineStr"/>
       <c r="D60" s="5" t="inlineStr"/>
       <c r="E60" s="6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2488,131 +2516,137 @@
       </c>
       <c r="C61" s="5" t="inlineStr"/>
       <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>194 dias</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>173 dias</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>143 dias</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>112 dias</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>82 dias</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>51 dias</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>20 dias</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="9" t="n">
-        <v>0</v>
+      <c r="C62" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr"/>
-      <c r="D63" s="9" t="inlineStr"/>
+      <c r="C63" s="10" t="inlineStr"/>
+      <c r="D63" s="10" t="inlineStr"/>
       <c r="E63" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F63" s="9" t="inlineStr"/>
-      <c r="G63" s="9" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr"/>
-      <c r="I63" s="9" t="inlineStr"/>
-      <c r="J63" s="9" t="inlineStr"/>
-      <c r="K63" s="9" t="inlineStr"/>
-      <c r="L63" s="9" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="F63" s="10" t="inlineStr"/>
+      <c r="G63" s="10" t="inlineStr"/>
+      <c r="H63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr"/>
+      <c r="M63" s="10" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="n"/>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="A64" s="11" t="n"/>
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr"/>
-      <c r="D64" s="9" t="inlineStr"/>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>70 dias</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr"/>
-      <c r="G64" s="9" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr"/>
-      <c r="I64" s="9" t="inlineStr"/>
-      <c r="J64" s="9" t="inlineStr"/>
-      <c r="K64" s="9" t="inlineStr"/>
-      <c r="L64" s="9" t="inlineStr"/>
-      <c r="M64" s="9" t="inlineStr"/>
-      <c r="N64" s="9" t="inlineStr"/>
+      <c r="C64" s="10" t="inlineStr"/>
+      <c r="D64" s="10" t="inlineStr"/>
+      <c r="E64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="10" t="inlineStr"/>
+      <c r="G64" s="10" t="inlineStr"/>
+      <c r="H64" s="10" t="inlineStr"/>
+      <c r="I64" s="10" t="inlineStr"/>
+      <c r="J64" s="10" t="inlineStr"/>
+      <c r="K64" s="10" t="inlineStr"/>
+      <c r="L64" s="10" t="inlineStr"/>
+      <c r="M64" s="10" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>ARARA AZUL 07/23  |  Cód: 13.67.0092  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 130X130  |  Coleção: P3  |  10</t>
+          <t>ARARA AZUL 07/23  |  Cód: 13.46.0176  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: P3  |  10</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -2621,40 +2655,40 @@
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2667,34 +2701,34 @@
       <c r="C67" s="5" t="inlineStr"/>
       <c r="D67" s="5" t="inlineStr"/>
       <c r="E67" s="6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
@@ -2706,129 +2740,149 @@
       </c>
       <c r="C68" s="5" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v>0</v>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>1102 dias</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>1081 dias</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>1051 dias</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>1020 dias</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>990 dias</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>959 dias</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>928 dias</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>898 dias</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>867 dias</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>837 dias</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>0</v>
+      <c r="C69" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="9" t="n">
+      <c r="F69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr"/>
+      <c r="C70" s="10" t="inlineStr"/>
+      <c r="D70" s="10" t="inlineStr"/>
       <c r="E70" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F70" s="9" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr"/>
-      <c r="L70" s="9" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr"/>
-      <c r="N70" s="9" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="F70" s="10" t="inlineStr"/>
+      <c r="G70" s="10" t="inlineStr"/>
+      <c r="H70" s="10" t="inlineStr"/>
+      <c r="I70" s="10" t="inlineStr"/>
+      <c r="J70" s="10" t="inlineStr"/>
+      <c r="K70" s="10" t="inlineStr"/>
+      <c r="L70" s="10" t="inlineStr"/>
+      <c r="M70" s="10" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="n"/>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="A71" s="11" t="n"/>
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr"/>
-      <c r="D71" s="9" t="inlineStr"/>
+      <c r="C71" s="10" t="inlineStr"/>
+      <c r="D71" s="10" t="inlineStr"/>
       <c r="E71" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="9" t="inlineStr"/>
-      <c r="G71" s="9" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr"/>
-      <c r="I71" s="9" t="inlineStr"/>
-      <c r="J71" s="9" t="inlineStr"/>
-      <c r="K71" s="9" t="inlineStr"/>
-      <c r="L71" s="9" t="inlineStr"/>
-      <c r="M71" s="9" t="inlineStr"/>
-      <c r="N71" s="9" t="inlineStr"/>
+      <c r="F71" s="10" t="inlineStr"/>
+      <c r="G71" s="10" t="inlineStr"/>
+      <c r="H71" s="10" t="inlineStr"/>
+      <c r="I71" s="10" t="inlineStr"/>
+      <c r="J71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr"/>
+      <c r="M71" s="10" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>AFRICA 05/22  |  Cód: 13.67.74  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 130X130  |  Coleção: M1  |  10</t>
+          <t>TIJUCA 08/23  |  Cód: 13.46.0177  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: Q1  |  10</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -2837,40 +2891,40 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -2883,34 +2937,34 @@
       <c r="C74" s="5" t="inlineStr"/>
       <c r="D74" s="5" t="inlineStr"/>
       <c r="E74" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H74" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2922,129 +2976,127 @@
       </c>
       <c r="C75" s="5" t="inlineStr"/>
       <c r="D75" s="5" t="inlineStr"/>
-      <c r="E75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>112 dias</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>91 dias</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>61 dias</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>30 dias</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr"/>
+      <c r="K75" s="5" t="inlineStr"/>
+      <c r="L75" s="5" t="inlineStr"/>
+      <c r="M75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="9" t="n">
-        <v>0</v>
+      <c r="C76" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr"/>
-      <c r="D77" s="9" t="inlineStr"/>
+      <c r="C77" s="10" t="inlineStr"/>
+      <c r="D77" s="10" t="inlineStr"/>
       <c r="E77" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
-      <c r="I77" s="9" t="inlineStr"/>
-      <c r="J77" s="9" t="inlineStr"/>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr"/>
-      <c r="N77" s="9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="F77" s="10" t="inlineStr"/>
+      <c r="G77" s="10" t="inlineStr"/>
+      <c r="H77" s="10" t="inlineStr"/>
+      <c r="I77" s="10" t="inlineStr"/>
+      <c r="J77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr"/>
+      <c r="M77" s="10" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="n"/>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="A78" s="11" t="n"/>
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr"/>
-      <c r="D78" s="9" t="inlineStr"/>
-      <c r="E78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="9" t="inlineStr"/>
-      <c r="G78" s="9" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr"/>
-      <c r="I78" s="9" t="inlineStr"/>
-      <c r="J78" s="9" t="inlineStr"/>
-      <c r="K78" s="9" t="inlineStr"/>
-      <c r="L78" s="9" t="inlineStr"/>
-      <c r="M78" s="9" t="inlineStr"/>
-      <c r="N78" s="9" t="inlineStr"/>
+      <c r="C78" s="10" t="inlineStr"/>
+      <c r="D78" s="10" t="inlineStr"/>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>70 dias</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr"/>
+      <c r="G78" s="10" t="inlineStr"/>
+      <c r="H78" s="10" t="inlineStr"/>
+      <c r="I78" s="10" t="inlineStr"/>
+      <c r="J78" s="10" t="inlineStr"/>
+      <c r="K78" s="10" t="inlineStr"/>
+      <c r="L78" s="10" t="inlineStr"/>
+      <c r="M78" s="10" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>AMAZONIA INDÍGENA 05/23  |  Cód: 45.14.0052  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O8  |  10</t>
+          <t>FAUNA BRASILEIRA 03/24  |  Cód: 13.46.0235  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 70X70  |  Coleção: R9  |  H5</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -3053,40 +3105,40 @@
         </is>
       </c>
       <c r="C80" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81">
@@ -3099,34 +3151,34 @@
       <c r="C81" s="5" t="inlineStr"/>
       <c r="D81" s="5" t="inlineStr"/>
       <c r="E81" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3138,129 +3190,117 @@
       </c>
       <c r="C82" s="5" t="inlineStr"/>
       <c r="D82" s="5" t="inlineStr"/>
-      <c r="E82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>33 dias</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>12 dias</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="9" t="n">
+      <c r="C83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="9" t="n">
+      <c r="F83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="9" t="inlineStr"/>
+      <c r="C84" s="10" t="inlineStr"/>
+      <c r="D84" s="10" t="inlineStr"/>
       <c r="E84" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F84" s="9" t="inlineStr"/>
-      <c r="G84" s="9" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
-      <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr"/>
-      <c r="L84" s="9" t="inlineStr"/>
-      <c r="M84" s="9" t="inlineStr"/>
-      <c r="N84" s="9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="F84" s="10" t="inlineStr"/>
+      <c r="G84" s="10" t="inlineStr"/>
+      <c r="H84" s="10" t="inlineStr"/>
+      <c r="I84" s="10" t="inlineStr"/>
+      <c r="J84" s="10" t="inlineStr"/>
+      <c r="K84" s="10" t="inlineStr"/>
+      <c r="L84" s="10" t="inlineStr"/>
+      <c r="M84" s="10" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="n"/>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="A85" s="11" t="n"/>
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr"/>
-      <c r="D85" s="9" t="inlineStr"/>
+      <c r="C85" s="10" t="inlineStr"/>
+      <c r="D85" s="10" t="inlineStr"/>
       <c r="E85" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F85" s="9" t="inlineStr"/>
-      <c r="G85" s="9" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
-      <c r="I85" s="9" t="inlineStr"/>
-      <c r="J85" s="9" t="inlineStr"/>
-      <c r="K85" s="9" t="inlineStr"/>
-      <c r="L85" s="9" t="inlineStr"/>
-      <c r="M85" s="9" t="inlineStr"/>
-      <c r="N85" s="9" t="inlineStr"/>
+      <c r="F85" s="10" t="inlineStr"/>
+      <c r="G85" s="10" t="inlineStr"/>
+      <c r="H85" s="10" t="inlineStr"/>
+      <c r="I85" s="10" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr"/>
+      <c r="M85" s="10" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>PANTANAL 05/23  |  Cód: 45.14.0055  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O8  |  10</t>
+          <t>GUARDIA DOS PORTAIS 04/24  |  Cód: 13.46.0246  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 70X70  |  Coleção: Q6  |  72</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -3269,40 +3309,40 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
@@ -3315,34 +3355,34 @@
       <c r="C88" s="5" t="inlineStr"/>
       <c r="D88" s="5" t="inlineStr"/>
       <c r="E88" s="6" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3354,131 +3394,119 @@
       </c>
       <c r="C89" s="5" t="inlineStr"/>
       <c r="D89" s="5" t="inlineStr"/>
-      <c r="E89" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>24 dias</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>24 dias</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr"/>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="5" t="inlineStr"/>
+      <c r="K89" s="5" t="inlineStr"/>
+      <c r="L89" s="5" t="inlineStr"/>
+      <c r="M89" s="5" t="inlineStr"/>
+      <c r="N89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="9" t="n">
-        <v>0</v>
+      <c r="C90" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr"/>
-      <c r="D91" s="9" t="inlineStr"/>
+      <c r="C91" s="10" t="inlineStr"/>
+      <c r="D91" s="10" t="inlineStr"/>
       <c r="E91" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="F91" s="9" t="inlineStr"/>
-      <c r="G91" s="9" t="inlineStr"/>
-      <c r="H91" s="9" t="inlineStr"/>
-      <c r="I91" s="9" t="inlineStr"/>
-      <c r="J91" s="9" t="inlineStr"/>
-      <c r="K91" s="9" t="inlineStr"/>
-      <c r="L91" s="9" t="inlineStr"/>
-      <c r="M91" s="9" t="inlineStr"/>
-      <c r="N91" s="9" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="F91" s="10" t="inlineStr"/>
+      <c r="G91" s="10" t="inlineStr"/>
+      <c r="H91" s="10" t="inlineStr"/>
+      <c r="I91" s="10" t="inlineStr"/>
+      <c r="J91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="inlineStr"/>
+      <c r="L91" s="10" t="inlineStr"/>
+      <c r="M91" s="10" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="n"/>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="A92" s="11" t="n"/>
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr"/>
-      <c r="D92" s="9" t="inlineStr"/>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>106 dias</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr"/>
-      <c r="G92" s="9" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr"/>
-      <c r="I92" s="9" t="inlineStr"/>
-      <c r="J92" s="9" t="inlineStr"/>
-      <c r="K92" s="9" t="inlineStr"/>
-      <c r="L92" s="9" t="inlineStr"/>
-      <c r="M92" s="9" t="inlineStr"/>
-      <c r="N92" s="9" t="inlineStr"/>
+      <c r="C92" s="10" t="inlineStr"/>
+      <c r="D92" s="10" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>65 dias</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr"/>
+      <c r="G92" s="10" t="inlineStr"/>
+      <c r="H92" s="10" t="inlineStr"/>
+      <c r="I92" s="10" t="inlineStr"/>
+      <c r="J92" s="10" t="inlineStr"/>
+      <c r="K92" s="10" t="inlineStr"/>
+      <c r="L92" s="10" t="inlineStr"/>
+      <c r="M92" s="10" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>CERRADO 05/23  |  Cód: 45.14.0053  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O7  |  116</t>
+          <t>ENCANTO CARIOCA 02/25  |  Cód: 13.46.0343  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  03</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -3487,40 +3515,40 @@
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -3533,34 +3561,34 @@
       <c r="C95" s="5" t="inlineStr"/>
       <c r="D95" s="5" t="inlineStr"/>
       <c r="E95" s="6" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3572,131 +3600,119 @@
       </c>
       <c r="C96" s="5" t="inlineStr"/>
       <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>43 dias</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>22 dias</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr"/>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="9" t="n">
-        <v>0</v>
+      <c r="C97" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="C98" s="10" t="inlineStr"/>
+      <c r="D98" s="10" t="inlineStr"/>
       <c r="E98" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="9" t="inlineStr"/>
-      <c r="G98" s="9" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
-      <c r="I98" s="9" t="inlineStr"/>
-      <c r="J98" s="9" t="inlineStr"/>
-      <c r="K98" s="9" t="inlineStr"/>
-      <c r="L98" s="9" t="inlineStr"/>
-      <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="F98" s="10" t="inlineStr"/>
+      <c r="G98" s="10" t="inlineStr"/>
+      <c r="H98" s="10" t="inlineStr"/>
+      <c r="I98" s="10" t="inlineStr"/>
+      <c r="J98" s="10" t="inlineStr"/>
+      <c r="K98" s="10" t="inlineStr"/>
+      <c r="L98" s="10" t="inlineStr"/>
+      <c r="M98" s="10" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="n"/>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="A99" s="11" t="n"/>
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr"/>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>10 dias</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr"/>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
-      <c r="I99" s="9" t="inlineStr"/>
-      <c r="J99" s="9" t="inlineStr"/>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="9" t="inlineStr"/>
+      <c r="C99" s="10" t="inlineStr"/>
+      <c r="D99" s="10" t="inlineStr"/>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>120 dias</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr"/>
+      <c r="G99" s="10" t="inlineStr"/>
+      <c r="H99" s="10" t="inlineStr"/>
+      <c r="I99" s="10" t="inlineStr"/>
+      <c r="J99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="inlineStr"/>
+      <c r="L99" s="10" t="inlineStr"/>
+      <c r="M99" s="10" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  18</t>
+          <t>PASSAPORTES DA ALEGRIA 02/25  |  Cód: 13.46.0347  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  03</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3751,34 +3767,34 @@
       <c r="C102" s="5" t="inlineStr"/>
       <c r="D102" s="5" t="inlineStr"/>
       <c r="E102" s="6" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -3823,96 +3839,98 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="9" t="n">
-        <v>0</v>
+      <c r="C104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr"/>
-      <c r="D105" s="9" t="inlineStr"/>
+      <c r="C105" s="10" t="inlineStr"/>
+      <c r="D105" s="10" t="inlineStr"/>
       <c r="E105" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="F105" s="9" t="inlineStr"/>
-      <c r="G105" s="9" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr"/>
-      <c r="I105" s="9" t="inlineStr"/>
-      <c r="J105" s="9" t="inlineStr"/>
-      <c r="K105" s="9" t="inlineStr"/>
-      <c r="L105" s="9" t="inlineStr"/>
-      <c r="M105" s="9" t="inlineStr"/>
-      <c r="N105" s="9" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="F105" s="10" t="inlineStr"/>
+      <c r="G105" s="10" t="inlineStr"/>
+      <c r="H105" s="10" t="inlineStr"/>
+      <c r="I105" s="10" t="inlineStr"/>
+      <c r="J105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="inlineStr"/>
+      <c r="L105" s="10" t="inlineStr"/>
+      <c r="M105" s="10" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="n"/>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="A106" s="11" t="n"/>
+      <c r="B106" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr"/>
-      <c r="D106" s="9" t="inlineStr"/>
-      <c r="E106" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="9" t="inlineStr"/>
-      <c r="G106" s="9" t="inlineStr"/>
-      <c r="H106" s="9" t="inlineStr"/>
-      <c r="I106" s="9" t="inlineStr"/>
-      <c r="J106" s="9" t="inlineStr"/>
-      <c r="K106" s="9" t="inlineStr"/>
-      <c r="L106" s="9" t="inlineStr"/>
-      <c r="M106" s="9" t="inlineStr"/>
-      <c r="N106" s="9" t="inlineStr"/>
+      <c r="C106" s="10" t="inlineStr"/>
+      <c r="D106" s="10" t="inlineStr"/>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr"/>
+      <c r="G106" s="10" t="inlineStr"/>
+      <c r="H106" s="10" t="inlineStr"/>
+      <c r="I106" s="10" t="inlineStr"/>
+      <c r="J106" s="10" t="inlineStr"/>
+      <c r="K106" s="10" t="inlineStr"/>
+      <c r="L106" s="10" t="inlineStr"/>
+      <c r="M106" s="10" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA PINK PURPLE 06/23  |  Cód: 45.14.0058  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O9  |  18</t>
+          <t>PASSAPORTES DA ALEGRIA 02/25  |  Cód: 13.46.0347  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  22</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -3921,40 +3939,40 @@
         </is>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -3967,34 +3985,34 @@
       <c r="C109" s="5" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
       <c r="E109" s="6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -4006,131 +4024,135 @@
       </c>
       <c r="C110" s="5" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>156 dias</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>135 dias</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>105 dias</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>74 dias</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>44 dias</t>
+        </is>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
+        <is>
+          <t>13 dias</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr"/>
+      <c r="L110" s="5" t="inlineStr"/>
+      <c r="M110" s="5" t="inlineStr"/>
+      <c r="N110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B111" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="9" t="n">
-        <v>0</v>
+      <c r="C111" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E111" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" s="9" t="n">
+      <c r="F111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B112" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr"/>
-      <c r="D112" s="9" t="inlineStr"/>
+      <c r="C112" s="10" t="inlineStr"/>
+      <c r="D112" s="10" t="inlineStr"/>
       <c r="E112" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="F112" s="9" t="inlineStr"/>
-      <c r="G112" s="9" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
-      <c r="I112" s="9" t="inlineStr"/>
-      <c r="J112" s="9" t="inlineStr"/>
-      <c r="K112" s="9" t="inlineStr"/>
-      <c r="L112" s="9" t="inlineStr"/>
-      <c r="M112" s="9" t="inlineStr"/>
-      <c r="N112" s="9" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F112" s="10" t="inlineStr"/>
+      <c r="G112" s="10" t="inlineStr"/>
+      <c r="H112" s="10" t="inlineStr"/>
+      <c r="I112" s="10" t="inlineStr"/>
+      <c r="J112" s="10" t="inlineStr"/>
+      <c r="K112" s="10" t="inlineStr"/>
+      <c r="L112" s="10" t="inlineStr"/>
+      <c r="M112" s="10" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="n"/>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="A113" s="11" t="n"/>
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr"/>
-      <c r="D113" s="9" t="inlineStr"/>
+      <c r="C113" s="10" t="inlineStr"/>
+      <c r="D113" s="10" t="inlineStr"/>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>140 dias</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr"/>
-      <c r="G113" s="9" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
-      <c r="I113" s="9" t="inlineStr"/>
-      <c r="J113" s="9" t="inlineStr"/>
-      <c r="K113" s="9" t="inlineStr"/>
-      <c r="L113" s="9" t="inlineStr"/>
-      <c r="M113" s="9" t="inlineStr"/>
-      <c r="N113" s="9" t="inlineStr"/>
+          <t>167 dias</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr"/>
+      <c r="G113" s="10" t="inlineStr"/>
+      <c r="H113" s="10" t="inlineStr"/>
+      <c r="I113" s="10" t="inlineStr"/>
+      <c r="J113" s="10" t="inlineStr"/>
+      <c r="K113" s="10" t="inlineStr"/>
+      <c r="L113" s="10" t="inlineStr"/>
+      <c r="M113" s="10" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>PASSAPORTES DA ALEGRIA 02/25  |  Cód: 13.46.0347  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  22</t>
+          <t>ENCANTO TROPICAL 03/25  |  Cód: 13.46.0371  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: U5  |  03</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -4139,40 +4161,40 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116">
@@ -4185,34 +4207,34 @@
       <c r="C116" s="5" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr"/>
       <c r="E116" s="6" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4224,131 +4246,127 @@
       </c>
       <c r="C117" s="5" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr"/>
-      <c r="E117" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>68 dias</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>68 dias</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>38 dias</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>7 dias</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="5" t="inlineStr"/>
+      <c r="K117" s="5" t="inlineStr"/>
+      <c r="L117" s="5" t="inlineStr"/>
+      <c r="M117" s="5" t="inlineStr"/>
+      <c r="N117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B118" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="9" t="n">
-        <v>0</v>
+      <c r="C118" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D118" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="E118" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" s="9" t="n">
+      <c r="F118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B119" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr"/>
-      <c r="D119" s="9" t="inlineStr"/>
+      <c r="C119" s="10" t="inlineStr"/>
+      <c r="D119" s="10" t="inlineStr"/>
       <c r="E119" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="F119" s="9" t="inlineStr"/>
-      <c r="G119" s="9" t="inlineStr"/>
-      <c r="H119" s="9" t="inlineStr"/>
-      <c r="I119" s="9" t="inlineStr"/>
-      <c r="J119" s="9" t="inlineStr"/>
-      <c r="K119" s="9" t="inlineStr"/>
-      <c r="L119" s="9" t="inlineStr"/>
-      <c r="M119" s="9" t="inlineStr"/>
-      <c r="N119" s="9" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="F119" s="10" t="inlineStr"/>
+      <c r="G119" s="10" t="inlineStr"/>
+      <c r="H119" s="10" t="inlineStr"/>
+      <c r="I119" s="10" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr"/>
+      <c r="K119" s="10" t="inlineStr"/>
+      <c r="L119" s="10" t="inlineStr"/>
+      <c r="M119" s="10" t="inlineStr"/>
+      <c r="N119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="n"/>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="A120" s="11" t="n"/>
+      <c r="B120" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr"/>
-      <c r="D120" s="9" t="inlineStr"/>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>167 dias</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr"/>
-      <c r="G120" s="9" t="inlineStr"/>
-      <c r="H120" s="9" t="inlineStr"/>
-      <c r="I120" s="9" t="inlineStr"/>
-      <c r="J120" s="9" t="inlineStr"/>
-      <c r="K120" s="9" t="inlineStr"/>
-      <c r="L120" s="9" t="inlineStr"/>
-      <c r="M120" s="9" t="inlineStr"/>
-      <c r="N120" s="9" t="inlineStr"/>
+      <c r="C120" s="10" t="inlineStr"/>
+      <c r="D120" s="10" t="inlineStr"/>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>77 dias</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr"/>
+      <c r="G120" s="10" t="inlineStr"/>
+      <c r="H120" s="10" t="inlineStr"/>
+      <c r="I120" s="10" t="inlineStr"/>
+      <c r="J120" s="10" t="inlineStr"/>
+      <c r="K120" s="10" t="inlineStr"/>
+      <c r="L120" s="10" t="inlineStr"/>
+      <c r="M120" s="10" t="inlineStr"/>
+      <c r="N120" s="10" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>ARARAS 04/2018  |  Cód: 14.15.22  |  Linha: LENÇOS  |  Subgrupo: GEORGETE DE POLIESTER  |  Grade: 130X200  |  Coleção: 67  |  40</t>
+          <t>ARARA AZUL 07/23  |  Cód: 13.67.0092  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 130X130  |  Coleção: P3  |  10</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -4357,40 +4375,40 @@
         </is>
       </c>
       <c r="C122" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -4403,34 +4421,34 @@
       <c r="C123" s="5" t="inlineStr"/>
       <c r="D123" s="5" t="inlineStr"/>
       <c r="E123" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>12</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4442,129 +4460,145 @@
       </c>
       <c r="C124" s="5" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>242 dias</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>221 dias</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>191 dias</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>160 dias</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>130 dias</t>
+        </is>
+      </c>
+      <c r="J124" s="8" t="inlineStr">
+        <is>
+          <t>99 dias</t>
+        </is>
+      </c>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>68 dias</t>
+        </is>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>38 dias</t>
+        </is>
+      </c>
+      <c r="M124" s="8" t="inlineStr">
+        <is>
+          <t>7 dias</t>
+        </is>
+      </c>
+      <c r="N124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="9" t="n">
-        <v>0</v>
+      <c r="C125" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E125" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" s="9" t="n">
+      <c r="F125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C126" s="9" t="inlineStr"/>
-      <c r="D126" s="9" t="inlineStr"/>
+      <c r="C126" s="10" t="inlineStr"/>
+      <c r="D126" s="10" t="inlineStr"/>
       <c r="E126" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F126" s="9" t="inlineStr"/>
-      <c r="G126" s="9" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
-      <c r="I126" s="9" t="inlineStr"/>
-      <c r="J126" s="9" t="inlineStr"/>
-      <c r="K126" s="9" t="inlineStr"/>
-      <c r="L126" s="9" t="inlineStr"/>
-      <c r="M126" s="9" t="inlineStr"/>
-      <c r="N126" s="9" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="F126" s="10" t="inlineStr"/>
+      <c r="G126" s="10" t="inlineStr"/>
+      <c r="H126" s="10" t="inlineStr"/>
+      <c r="I126" s="10" t="inlineStr"/>
+      <c r="J126" s="10" t="inlineStr"/>
+      <c r="K126" s="10" t="inlineStr"/>
+      <c r="L126" s="10" t="inlineStr"/>
+      <c r="M126" s="10" t="inlineStr"/>
+      <c r="N126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="10" t="n"/>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="A127" s="11" t="n"/>
+      <c r="B127" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr"/>
-      <c r="D127" s="9" t="inlineStr"/>
+      <c r="C127" s="10" t="inlineStr"/>
+      <c r="D127" s="10" t="inlineStr"/>
       <c r="E127" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="9" t="inlineStr"/>
-      <c r="G127" s="9" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr"/>
-      <c r="I127" s="9" t="inlineStr"/>
-      <c r="J127" s="9" t="inlineStr"/>
-      <c r="K127" s="9" t="inlineStr"/>
-      <c r="L127" s="9" t="inlineStr"/>
-      <c r="M127" s="9" t="inlineStr"/>
-      <c r="N127" s="9" t="inlineStr"/>
+      <c r="F127" s="10" t="inlineStr"/>
+      <c r="G127" s="10" t="inlineStr"/>
+      <c r="H127" s="10" t="inlineStr"/>
+      <c r="I127" s="10" t="inlineStr"/>
+      <c r="J127" s="10" t="inlineStr"/>
+      <c r="K127" s="10" t="inlineStr"/>
+      <c r="L127" s="10" t="inlineStr"/>
+      <c r="M127" s="10" t="inlineStr"/>
+      <c r="N127" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>AMAZONIA INDÍGENA 05/23  |  Cód: 45.14.0052  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O8  |  40</t>
+          <t>AFRICA 05/22  |  Cód: 13.67.74  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 130X130  |  Coleção: M1  |  10</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -4573,40 +4607,40 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130">
@@ -4619,34 +4653,34 @@
       <c r="C130" s="5" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="6" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -4658,131 +4692,113 @@
       </c>
       <c r="C131" s="5" t="inlineStr"/>
       <c r="D131" s="5" t="inlineStr"/>
-      <c r="E131" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+      <c r="J131" s="5" t="inlineStr"/>
+      <c r="K131" s="5" t="inlineStr"/>
+      <c r="L131" s="5" t="inlineStr"/>
+      <c r="M131" s="5" t="inlineStr"/>
+      <c r="N131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="B132" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="9" t="n">
-        <v>0</v>
+      <c r="C132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr"/>
-      <c r="D133" s="9" t="inlineStr"/>
+      <c r="C133" s="10" t="inlineStr"/>
+      <c r="D133" s="10" t="inlineStr"/>
       <c r="E133" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="F133" s="9" t="inlineStr"/>
-      <c r="G133" s="9" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
-      <c r="I133" s="9" t="inlineStr"/>
-      <c r="J133" s="9" t="inlineStr"/>
-      <c r="K133" s="9" t="inlineStr"/>
-      <c r="L133" s="9" t="inlineStr"/>
-      <c r="M133" s="9" t="inlineStr"/>
-      <c r="N133" s="9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F133" s="10" t="inlineStr"/>
+      <c r="G133" s="10" t="inlineStr"/>
+      <c r="H133" s="10" t="inlineStr"/>
+      <c r="I133" s="10" t="inlineStr"/>
+      <c r="J133" s="10" t="inlineStr"/>
+      <c r="K133" s="10" t="inlineStr"/>
+      <c r="L133" s="10" t="inlineStr"/>
+      <c r="M133" s="10" t="inlineStr"/>
+      <c r="N133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="n"/>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="A134" s="11" t="n"/>
+      <c r="B134" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr"/>
-      <c r="D134" s="9" t="inlineStr"/>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>137 dias</t>
-        </is>
-      </c>
-      <c r="F134" s="9" t="inlineStr"/>
-      <c r="G134" s="9" t="inlineStr"/>
-      <c r="H134" s="9" t="inlineStr"/>
-      <c r="I134" s="9" t="inlineStr"/>
-      <c r="J134" s="9" t="inlineStr"/>
-      <c r="K134" s="9" t="inlineStr"/>
-      <c r="L134" s="9" t="inlineStr"/>
-      <c r="M134" s="9" t="inlineStr"/>
-      <c r="N134" s="9" t="inlineStr"/>
+      <c r="C134" s="10" t="inlineStr"/>
+      <c r="D134" s="10" t="inlineStr"/>
+      <c r="E134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="10" t="inlineStr"/>
+      <c r="G134" s="10" t="inlineStr"/>
+      <c r="H134" s="10" t="inlineStr"/>
+      <c r="I134" s="10" t="inlineStr"/>
+      <c r="J134" s="10" t="inlineStr"/>
+      <c r="K134" s="10" t="inlineStr"/>
+      <c r="L134" s="10" t="inlineStr"/>
+      <c r="M134" s="10" t="inlineStr"/>
+      <c r="N134" s="10" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  42</t>
+          <t>ARARAS 04/2018  |  Cód: 14.15.22  |  Linha: LENÇOS  |  Subgrupo: GEORGETE DE POLIESTER  |  Grade: 130X200  |  Coleção: 67  |  40</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -4791,40 +4807,40 @@
         </is>
       </c>
       <c r="C136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -4837,34 +4853,34 @@
       <c r="C137" s="5" t="inlineStr"/>
       <c r="D137" s="5" t="inlineStr"/>
       <c r="E137" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -4876,131 +4892,133 @@
       </c>
       <c r="C138" s="5" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>174 dias</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>153 dias</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>123 dias</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>92 dias</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>62 dias</t>
+        </is>
+      </c>
+      <c r="J138" s="8" t="inlineStr">
+        <is>
+          <t>31 dias</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr"/>
+      <c r="L138" s="5" t="inlineStr"/>
+      <c r="M138" s="5" t="inlineStr"/>
+      <c r="N138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B139" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="9" t="n">
-        <v>0</v>
+      <c r="C139" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D139" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B140" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C140" s="9" t="inlineStr"/>
-      <c r="D140" s="9" t="inlineStr"/>
+      <c r="C140" s="10" t="inlineStr"/>
+      <c r="D140" s="10" t="inlineStr"/>
       <c r="E140" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F140" s="9" t="inlineStr"/>
-      <c r="G140" s="9" t="inlineStr"/>
-      <c r="H140" s="9" t="inlineStr"/>
-      <c r="I140" s="9" t="inlineStr"/>
-      <c r="J140" s="9" t="inlineStr"/>
-      <c r="K140" s="9" t="inlineStr"/>
-      <c r="L140" s="9" t="inlineStr"/>
-      <c r="M140" s="9" t="inlineStr"/>
-      <c r="N140" s="9" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="F140" s="10" t="inlineStr"/>
+      <c r="G140" s="10" t="inlineStr"/>
+      <c r="H140" s="10" t="inlineStr"/>
+      <c r="I140" s="10" t="inlineStr"/>
+      <c r="J140" s="10" t="inlineStr"/>
+      <c r="K140" s="10" t="inlineStr"/>
+      <c r="L140" s="10" t="inlineStr"/>
+      <c r="M140" s="10" t="inlineStr"/>
+      <c r="N140" s="10" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="10" t="n"/>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="A141" s="11" t="n"/>
+      <c r="B141" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C141" s="9" t="inlineStr"/>
-      <c r="D141" s="9" t="inlineStr"/>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>25 dias</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr"/>
-      <c r="G141" s="9" t="inlineStr"/>
-      <c r="H141" s="9" t="inlineStr"/>
-      <c r="I141" s="9" t="inlineStr"/>
-      <c r="J141" s="9" t="inlineStr"/>
-      <c r="K141" s="9" t="inlineStr"/>
-      <c r="L141" s="9" t="inlineStr"/>
-      <c r="M141" s="9" t="inlineStr"/>
-      <c r="N141" s="9" t="inlineStr"/>
+      <c r="C141" s="10" t="inlineStr"/>
+      <c r="D141" s="10" t="inlineStr"/>
+      <c r="E141" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="10" t="inlineStr"/>
+      <c r="G141" s="10" t="inlineStr"/>
+      <c r="H141" s="10" t="inlineStr"/>
+      <c r="I141" s="10" t="inlineStr"/>
+      <c r="J141" s="10" t="inlineStr"/>
+      <c r="K141" s="10" t="inlineStr"/>
+      <c r="L141" s="10" t="inlineStr"/>
+      <c r="M141" s="10" t="inlineStr"/>
+      <c r="N141" s="10" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  47</t>
+          <t>BRASIL TROPICAL 12/22  |  Cód: 45.14.0035  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O2  |  C6</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -5009,40 +5027,40 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E143" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M143" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144">
@@ -5055,34 +5073,34 @@
       <c r="C144" s="5" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr"/>
       <c r="E144" s="6" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M144" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -5094,129 +5112,131 @@
       </c>
       <c r="C145" s="5" t="inlineStr"/>
       <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>121 dias</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>100 dias</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>70 dias</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>39 dias</t>
+        </is>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>9 dias</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr"/>
+      <c r="K145" s="5" t="inlineStr"/>
+      <c r="L145" s="5" t="inlineStr"/>
+      <c r="M145" s="5" t="inlineStr"/>
+      <c r="N145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B146" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="9" t="n">
-        <v>0</v>
+      <c r="C146" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D146" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B147" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C147" s="9" t="inlineStr"/>
-      <c r="D147" s="9" t="inlineStr"/>
+      <c r="C147" s="10" t="inlineStr"/>
+      <c r="D147" s="10" t="inlineStr"/>
       <c r="E147" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="F147" s="9" t="inlineStr"/>
-      <c r="G147" s="9" t="inlineStr"/>
-      <c r="H147" s="9" t="inlineStr"/>
-      <c r="I147" s="9" t="inlineStr"/>
-      <c r="J147" s="9" t="inlineStr"/>
-      <c r="K147" s="9" t="inlineStr"/>
-      <c r="L147" s="9" t="inlineStr"/>
-      <c r="M147" s="9" t="inlineStr"/>
-      <c r="N147" s="9" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="F147" s="10" t="inlineStr"/>
+      <c r="G147" s="10" t="inlineStr"/>
+      <c r="H147" s="10" t="inlineStr"/>
+      <c r="I147" s="10" t="inlineStr"/>
+      <c r="J147" s="10" t="inlineStr"/>
+      <c r="K147" s="10" t="inlineStr"/>
+      <c r="L147" s="10" t="inlineStr"/>
+      <c r="M147" s="10" t="inlineStr"/>
+      <c r="N147" s="10" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="10" t="n"/>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="A148" s="11" t="n"/>
+      <c r="B148" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C148" s="9" t="inlineStr"/>
-      <c r="D148" s="9" t="inlineStr"/>
-      <c r="E148" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" s="9" t="inlineStr"/>
-      <c r="G148" s="9" t="inlineStr"/>
-      <c r="H148" s="9" t="inlineStr"/>
-      <c r="I148" s="9" t="inlineStr"/>
-      <c r="J148" s="9" t="inlineStr"/>
-      <c r="K148" s="9" t="inlineStr"/>
-      <c r="L148" s="9" t="inlineStr"/>
-      <c r="M148" s="9" t="inlineStr"/>
-      <c r="N148" s="9" t="inlineStr"/>
+      <c r="C148" s="10" t="inlineStr"/>
+      <c r="D148" s="10" t="inlineStr"/>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>370 dias</t>
+        </is>
+      </c>
+      <c r="F148" s="10" t="inlineStr"/>
+      <c r="G148" s="10" t="inlineStr"/>
+      <c r="H148" s="10" t="inlineStr"/>
+      <c r="I148" s="10" t="inlineStr"/>
+      <c r="J148" s="10" t="inlineStr"/>
+      <c r="K148" s="10" t="inlineStr"/>
+      <c r="L148" s="10" t="inlineStr"/>
+      <c r="M148" s="10" t="inlineStr"/>
+      <c r="N148" s="10" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA PINK PURPLE 06/23  |  Cód: 45.14.0058  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O9  |  47</t>
+          <t>BRASIL ANIMAL PRINT 12/22  |  Cód: 45.14.0036  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O2  |  C6</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -5225,40 +5245,40 @@
         </is>
       </c>
       <c r="C150" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J150" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M150" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="151">
@@ -5271,34 +5291,34 @@
       <c r="C151" s="5" t="inlineStr"/>
       <c r="D151" s="5" t="inlineStr"/>
       <c r="E151" s="6" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="M151" s="5" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="152">
@@ -5310,129 +5330,151 @@
       </c>
       <c r="C152" s="5" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr"/>
-      <c r="E152" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" s="5" t="n">
-        <v>0</v>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>300 dias</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>279 dias</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>249 dias</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>218 dias</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>188 dias</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>157 dias</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>126 dias</t>
+        </is>
+      </c>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>96 dias</t>
+        </is>
+      </c>
+      <c r="M152" s="8" t="inlineStr">
+        <is>
+          <t>65 dias</t>
+        </is>
+      </c>
+      <c r="N152" s="8" t="inlineStr">
+        <is>
+          <t>35 dias</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B153" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="9" t="n">
-        <v>0</v>
+      <c r="C153" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D153" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="E153" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B154" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr"/>
-      <c r="D154" s="9" t="inlineStr"/>
+      <c r="C154" s="10" t="inlineStr"/>
+      <c r="D154" s="10" t="inlineStr"/>
       <c r="E154" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F154" s="9" t="inlineStr"/>
-      <c r="G154" s="9" t="inlineStr"/>
-      <c r="H154" s="9" t="inlineStr"/>
-      <c r="I154" s="9" t="inlineStr"/>
-      <c r="J154" s="9" t="inlineStr"/>
-      <c r="K154" s="9" t="inlineStr"/>
-      <c r="L154" s="9" t="inlineStr"/>
-      <c r="M154" s="9" t="inlineStr"/>
-      <c r="N154" s="9" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="F154" s="10" t="inlineStr"/>
+      <c r="G154" s="10" t="inlineStr"/>
+      <c r="H154" s="10" t="inlineStr"/>
+      <c r="I154" s="10" t="inlineStr"/>
+      <c r="J154" s="10" t="inlineStr"/>
+      <c r="K154" s="10" t="inlineStr"/>
+      <c r="L154" s="10" t="inlineStr"/>
+      <c r="M154" s="10" t="inlineStr"/>
+      <c r="N154" s="10" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="10" t="n"/>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="A155" s="11" t="n"/>
+      <c r="B155" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C155" s="9" t="inlineStr"/>
-      <c r="D155" s="9" t="inlineStr"/>
-      <c r="E155" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="9" t="inlineStr"/>
-      <c r="G155" s="9" t="inlineStr"/>
-      <c r="H155" s="9" t="inlineStr"/>
-      <c r="I155" s="9" t="inlineStr"/>
-      <c r="J155" s="9" t="inlineStr"/>
-      <c r="K155" s="9" t="inlineStr"/>
-      <c r="L155" s="9" t="inlineStr"/>
-      <c r="M155" s="9" t="inlineStr"/>
-      <c r="N155" s="9" t="inlineStr"/>
+      <c r="C155" s="10" t="inlineStr"/>
+      <c r="D155" s="10" t="inlineStr"/>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>147 dias</t>
+        </is>
+      </c>
+      <c r="F155" s="10" t="inlineStr"/>
+      <c r="G155" s="10" t="inlineStr"/>
+      <c r="H155" s="10" t="inlineStr"/>
+      <c r="I155" s="10" t="inlineStr"/>
+      <c r="J155" s="10" t="inlineStr"/>
+      <c r="K155" s="10" t="inlineStr"/>
+      <c r="L155" s="10" t="inlineStr"/>
+      <c r="M155" s="10" t="inlineStr"/>
+      <c r="N155" s="10" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>GUARDIA DOS PORTAIS 04/24  |  Cód: 13.46.0246  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 70X70  |  Coleção: Q6  |  72</t>
+          <t>AMAZONIA INDÍGENA 05/23  |  Cód: 45.14.0052  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O8  |  10</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -5441,40 +5483,40 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E157" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K157" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M157" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -5487,34 +5529,34 @@
       <c r="C158" s="5" t="inlineStr"/>
       <c r="D158" s="5" t="inlineStr"/>
       <c r="E158" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J158" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K158" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -5526,131 +5568,121 @@
       </c>
       <c r="C159" s="5" t="inlineStr"/>
       <c r="D159" s="5" t="inlineStr"/>
-      <c r="E159" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>67 dias</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>46 dias</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>16 dias</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr"/>
+      <c r="J159" s="5" t="inlineStr"/>
+      <c r="K159" s="5" t="inlineStr"/>
+      <c r="L159" s="5" t="inlineStr"/>
+      <c r="M159" s="5" t="inlineStr"/>
+      <c r="N159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B160" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="9" t="n">
-        <v>0</v>
+      <c r="C160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B161" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C161" s="9" t="inlineStr"/>
-      <c r="D161" s="9" t="inlineStr"/>
+      <c r="C161" s="10" t="inlineStr"/>
+      <c r="D161" s="10" t="inlineStr"/>
       <c r="E161" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F161" s="9" t="inlineStr"/>
-      <c r="G161" s="9" t="inlineStr"/>
-      <c r="H161" s="9" t="inlineStr"/>
-      <c r="I161" s="9" t="inlineStr"/>
-      <c r="J161" s="9" t="inlineStr"/>
-      <c r="K161" s="9" t="inlineStr"/>
-      <c r="L161" s="9" t="inlineStr"/>
-      <c r="M161" s="9" t="inlineStr"/>
-      <c r="N161" s="9" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="F161" s="10" t="inlineStr"/>
+      <c r="G161" s="10" t="inlineStr"/>
+      <c r="H161" s="10" t="inlineStr"/>
+      <c r="I161" s="10" t="inlineStr"/>
+      <c r="J161" s="10" t="inlineStr"/>
+      <c r="K161" s="10" t="inlineStr"/>
+      <c r="L161" s="10" t="inlineStr"/>
+      <c r="M161" s="10" t="inlineStr"/>
+      <c r="N161" s="10" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="10" t="n"/>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="A162" s="11" t="n"/>
+      <c r="B162" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C162" s="9" t="inlineStr"/>
-      <c r="D162" s="9" t="inlineStr"/>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>65 dias</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr"/>
-      <c r="G162" s="9" t="inlineStr"/>
-      <c r="H162" s="9" t="inlineStr"/>
-      <c r="I162" s="9" t="inlineStr"/>
-      <c r="J162" s="9" t="inlineStr"/>
-      <c r="K162" s="9" t="inlineStr"/>
-      <c r="L162" s="9" t="inlineStr"/>
-      <c r="M162" s="9" t="inlineStr"/>
-      <c r="N162" s="9" t="inlineStr"/>
+      <c r="C162" s="10" t="inlineStr"/>
+      <c r="D162" s="10" t="inlineStr"/>
+      <c r="E162" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="10" t="inlineStr"/>
+      <c r="G162" s="10" t="inlineStr"/>
+      <c r="H162" s="10" t="inlineStr"/>
+      <c r="I162" s="10" t="inlineStr"/>
+      <c r="J162" s="10" t="inlineStr"/>
+      <c r="K162" s="10" t="inlineStr"/>
+      <c r="L162" s="10" t="inlineStr"/>
+      <c r="M162" s="10" t="inlineStr"/>
+      <c r="N162" s="10" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>BRASIL ANIMAL PRINT 22  |  Cód: 13.46.0067  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: M6  |  C6</t>
+          <t>AMAZONIA INDÍGENA 05/23  |  Cód: 45.14.0052  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O8  |  40</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -5659,40 +5691,40 @@
         </is>
       </c>
       <c r="C164" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M164" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165">
@@ -5705,34 +5737,34 @@
       <c r="C165" s="5" t="inlineStr"/>
       <c r="D165" s="5" t="inlineStr"/>
       <c r="E165" s="6" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="J165" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K165" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M165" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -5744,131 +5776,131 @@
       </c>
       <c r="C166" s="5" t="inlineStr"/>
       <c r="D166" s="5" t="inlineStr"/>
-      <c r="E166" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="F166" s="8" t="inlineStr">
+        <is>
+          <t>115 dias</t>
+        </is>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>85 dias</t>
+        </is>
+      </c>
+      <c r="H166" s="8" t="inlineStr">
+        <is>
+          <t>54 dias</t>
+        </is>
+      </c>
+      <c r="I166" s="8" t="inlineStr">
+        <is>
+          <t>24 dias</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr"/>
+      <c r="K166" s="5" t="inlineStr"/>
+      <c r="L166" s="5" t="inlineStr"/>
+      <c r="M166" s="5" t="inlineStr"/>
+      <c r="N166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B167" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" s="9" t="n">
-        <v>0</v>
+      <c r="C167" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D167" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E167" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C168" s="9" t="inlineStr"/>
-      <c r="D168" s="9" t="inlineStr"/>
+      <c r="C168" s="10" t="inlineStr"/>
+      <c r="D168" s="10" t="inlineStr"/>
       <c r="E168" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="F168" s="9" t="inlineStr"/>
-      <c r="G168" s="9" t="inlineStr"/>
-      <c r="H168" s="9" t="inlineStr"/>
-      <c r="I168" s="9" t="inlineStr"/>
-      <c r="J168" s="9" t="inlineStr"/>
-      <c r="K168" s="9" t="inlineStr"/>
-      <c r="L168" s="9" t="inlineStr"/>
-      <c r="M168" s="9" t="inlineStr"/>
-      <c r="N168" s="9" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="F168" s="10" t="inlineStr"/>
+      <c r="G168" s="10" t="inlineStr"/>
+      <c r="H168" s="10" t="inlineStr"/>
+      <c r="I168" s="10" t="inlineStr"/>
+      <c r="J168" s="10" t="inlineStr"/>
+      <c r="K168" s="10" t="inlineStr"/>
+      <c r="L168" s="10" t="inlineStr"/>
+      <c r="M168" s="10" t="inlineStr"/>
+      <c r="N168" s="10" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="10" t="n"/>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="A169" s="11" t="n"/>
+      <c r="B169" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr"/>
-      <c r="D169" s="9" t="inlineStr"/>
+      <c r="C169" s="10" t="inlineStr"/>
+      <c r="D169" s="10" t="inlineStr"/>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>310 dias</t>
-        </is>
-      </c>
-      <c r="F169" s="9" t="inlineStr"/>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr"/>
-      <c r="I169" s="9" t="inlineStr"/>
-      <c r="J169" s="9" t="inlineStr"/>
-      <c r="K169" s="9" t="inlineStr"/>
-      <c r="L169" s="9" t="inlineStr"/>
-      <c r="M169" s="9" t="inlineStr"/>
-      <c r="N169" s="9" t="inlineStr"/>
+          <t>137 dias</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr"/>
+      <c r="G169" s="10" t="inlineStr"/>
+      <c r="H169" s="10" t="inlineStr"/>
+      <c r="I169" s="10" t="inlineStr"/>
+      <c r="J169" s="10" t="inlineStr"/>
+      <c r="K169" s="10" t="inlineStr"/>
+      <c r="L169" s="10" t="inlineStr"/>
+      <c r="M169" s="10" t="inlineStr"/>
+      <c r="N169" s="10" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>BRASIL TROPICAL 12/22  |  Cód: 45.14.0035  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O2  |  C6</t>
+          <t>CERRADO 05/23  |  Cód: 45.14.0053  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O7  |  116</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -5877,40 +5909,40 @@
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E171" s="6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K171" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M171" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N171" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -5923,34 +5955,34 @@
       <c r="C172" s="5" t="inlineStr"/>
       <c r="D172" s="5" t="inlineStr"/>
       <c r="E172" s="6" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -5962,131 +5994,115 @@
       </c>
       <c r="C173" s="5" t="inlineStr"/>
       <c r="D173" s="5" t="inlineStr"/>
-      <c r="E173" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N173" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>1 dias</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr"/>
+      <c r="G173" s="5" t="inlineStr"/>
+      <c r="H173" s="5" t="inlineStr"/>
+      <c r="I173" s="5" t="inlineStr"/>
+      <c r="J173" s="5" t="inlineStr"/>
+      <c r="K173" s="5" t="inlineStr"/>
+      <c r="L173" s="5" t="inlineStr"/>
+      <c r="M173" s="5" t="inlineStr"/>
+      <c r="N173" s="5" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B174" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="9" t="n">
-        <v>0</v>
+      <c r="C174" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E174" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N174" s="9" t="n">
+      <c r="F174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B175" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C175" s="9" t="inlineStr"/>
-      <c r="D175" s="9" t="inlineStr"/>
+      <c r="C175" s="10" t="inlineStr"/>
+      <c r="D175" s="10" t="inlineStr"/>
       <c r="E175" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="F175" s="9" t="inlineStr"/>
-      <c r="G175" s="9" t="inlineStr"/>
-      <c r="H175" s="9" t="inlineStr"/>
-      <c r="I175" s="9" t="inlineStr"/>
-      <c r="J175" s="9" t="inlineStr"/>
-      <c r="K175" s="9" t="inlineStr"/>
-      <c r="L175" s="9" t="inlineStr"/>
-      <c r="M175" s="9" t="inlineStr"/>
-      <c r="N175" s="9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F175" s="10" t="inlineStr"/>
+      <c r="G175" s="10" t="inlineStr"/>
+      <c r="H175" s="10" t="inlineStr"/>
+      <c r="I175" s="10" t="inlineStr"/>
+      <c r="J175" s="10" t="inlineStr"/>
+      <c r="K175" s="10" t="inlineStr"/>
+      <c r="L175" s="10" t="inlineStr"/>
+      <c r="M175" s="10" t="inlineStr"/>
+      <c r="N175" s="10" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="10" t="n"/>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="A176" s="11" t="n"/>
+      <c r="B176" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C176" s="9" t="inlineStr"/>
-      <c r="D176" s="9" t="inlineStr"/>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>370 dias</t>
-        </is>
-      </c>
-      <c r="F176" s="9" t="inlineStr"/>
-      <c r="G176" s="9" t="inlineStr"/>
-      <c r="H176" s="9" t="inlineStr"/>
-      <c r="I176" s="9" t="inlineStr"/>
-      <c r="J176" s="9" t="inlineStr"/>
-      <c r="K176" s="9" t="inlineStr"/>
-      <c r="L176" s="9" t="inlineStr"/>
-      <c r="M176" s="9" t="inlineStr"/>
-      <c r="N176" s="9" t="inlineStr"/>
+      <c r="C176" s="10" t="inlineStr"/>
+      <c r="D176" s="10" t="inlineStr"/>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>10 dias</t>
+        </is>
+      </c>
+      <c r="F176" s="10" t="inlineStr"/>
+      <c r="G176" s="10" t="inlineStr"/>
+      <c r="H176" s="10" t="inlineStr"/>
+      <c r="I176" s="10" t="inlineStr"/>
+      <c r="J176" s="10" t="inlineStr"/>
+      <c r="K176" s="10" t="inlineStr"/>
+      <c r="L176" s="10" t="inlineStr"/>
+      <c r="M176" s="10" t="inlineStr"/>
+      <c r="N176" s="10" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>BRASIL ANIMAL PRINT 12/22  |  Cód: 45.14.0036  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O2  |  C6</t>
+          <t>PANTANAL 05/23  |  Cód: 45.14.0055  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O8  |  10</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -6095,40 +6111,40 @@
         </is>
       </c>
       <c r="C178" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E178" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H178" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J178" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K178" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M178" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N178" s="5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="179">
@@ -6141,34 +6157,34 @@
       <c r="C179" s="5" t="inlineStr"/>
       <c r="D179" s="5" t="inlineStr"/>
       <c r="E179" s="6" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H179" s="5" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="K179" s="5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M179" s="5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -6180,131 +6196,135 @@
       </c>
       <c r="C180" s="5" t="inlineStr"/>
       <c r="D180" s="5" t="inlineStr"/>
-      <c r="E180" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>167 dias</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>146 dias</t>
+        </is>
+      </c>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>116 dias</t>
+        </is>
+      </c>
+      <c r="H180" s="8" t="inlineStr">
+        <is>
+          <t>85 dias</t>
+        </is>
+      </c>
+      <c r="I180" s="8" t="inlineStr">
+        <is>
+          <t>55 dias</t>
+        </is>
+      </c>
+      <c r="J180" s="8" t="inlineStr">
+        <is>
+          <t>24 dias</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="inlineStr"/>
+      <c r="L180" s="5" t="inlineStr"/>
+      <c r="M180" s="5" t="inlineStr"/>
+      <c r="N180" s="5" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B181" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" s="9" t="n">
-        <v>0</v>
+      <c r="C181" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D181" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="E181" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B182" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C182" s="9" t="inlineStr"/>
-      <c r="D182" s="9" t="inlineStr"/>
+      <c r="C182" s="10" t="inlineStr"/>
+      <c r="D182" s="10" t="inlineStr"/>
       <c r="E182" s="6" t="n">
-        <v>88</v>
-      </c>
-      <c r="F182" s="9" t="inlineStr"/>
-      <c r="G182" s="9" t="inlineStr"/>
-      <c r="H182" s="9" t="inlineStr"/>
-      <c r="I182" s="9" t="inlineStr"/>
-      <c r="J182" s="9" t="inlineStr"/>
-      <c r="K182" s="9" t="inlineStr"/>
-      <c r="L182" s="9" t="inlineStr"/>
-      <c r="M182" s="9" t="inlineStr"/>
-      <c r="N182" s="9" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="F182" s="10" t="inlineStr"/>
+      <c r="G182" s="10" t="inlineStr"/>
+      <c r="H182" s="10" t="inlineStr"/>
+      <c r="I182" s="10" t="inlineStr"/>
+      <c r="J182" s="10" t="inlineStr"/>
+      <c r="K182" s="10" t="inlineStr"/>
+      <c r="L182" s="10" t="inlineStr"/>
+      <c r="M182" s="10" t="inlineStr"/>
+      <c r="N182" s="10" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="10" t="n"/>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="A183" s="11" t="n"/>
+      <c r="B183" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr"/>
-      <c r="D183" s="9" t="inlineStr"/>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>147 dias</t>
-        </is>
-      </c>
-      <c r="F183" s="9" t="inlineStr"/>
-      <c r="G183" s="9" t="inlineStr"/>
-      <c r="H183" s="9" t="inlineStr"/>
-      <c r="I183" s="9" t="inlineStr"/>
-      <c r="J183" s="9" t="inlineStr"/>
-      <c r="K183" s="9" t="inlineStr"/>
-      <c r="L183" s="9" t="inlineStr"/>
-      <c r="M183" s="9" t="inlineStr"/>
-      <c r="N183" s="9" t="inlineStr"/>
+      <c r="C183" s="10" t="inlineStr"/>
+      <c r="D183" s="10" t="inlineStr"/>
+      <c r="E183" s="8" t="inlineStr">
+        <is>
+          <t>106 dias</t>
+        </is>
+      </c>
+      <c r="F183" s="10" t="inlineStr"/>
+      <c r="G183" s="10" t="inlineStr"/>
+      <c r="H183" s="10" t="inlineStr"/>
+      <c r="I183" s="10" t="inlineStr"/>
+      <c r="J183" s="10" t="inlineStr"/>
+      <c r="K183" s="10" t="inlineStr"/>
+      <c r="L183" s="10" t="inlineStr"/>
+      <c r="M183" s="10" t="inlineStr"/>
+      <c r="N183" s="10" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>FAUNA BRASILEIRA 03/24  |  Cód: 13.46.0235  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 70X70  |  Coleção: R9  |  H5</t>
+          <t>RAMOS DE PURPURA PINK PURPLE 06/23  |  Cód: 45.14.0058  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O9  |  18</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -6313,40 +6333,40 @@
         </is>
       </c>
       <c r="C185" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E185" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J185" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M185" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N185" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186">
@@ -6359,34 +6379,34 @@
       <c r="C186" s="5" t="inlineStr"/>
       <c r="D186" s="5" t="inlineStr"/>
       <c r="E186" s="6" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J186" s="5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K186" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M186" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N186" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187">
@@ -6398,129 +6418,151 @@
       </c>
       <c r="C187" s="5" t="inlineStr"/>
       <c r="D187" s="5" t="inlineStr"/>
-      <c r="E187" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N187" s="5" t="n">
-        <v>0</v>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>276 dias</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>255 dias</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>225 dias</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>194 dias</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>164 dias</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>133 dias</t>
+        </is>
+      </c>
+      <c r="K187" s="8" t="inlineStr">
+        <is>
+          <t>102 dias</t>
+        </is>
+      </c>
+      <c r="L187" s="8" t="inlineStr">
+        <is>
+          <t>72 dias</t>
+        </is>
+      </c>
+      <c r="M187" s="8" t="inlineStr">
+        <is>
+          <t>41 dias</t>
+        </is>
+      </c>
+      <c r="N187" s="8" t="inlineStr">
+        <is>
+          <t>11 dias</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B188" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D188" s="9" t="n">
-        <v>0</v>
+      <c r="C188" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B189" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C189" s="9" t="inlineStr"/>
-      <c r="D189" s="9" t="inlineStr"/>
+      <c r="C189" s="10" t="inlineStr"/>
+      <c r="D189" s="10" t="inlineStr"/>
       <c r="E189" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F189" s="9" t="inlineStr"/>
-      <c r="G189" s="9" t="inlineStr"/>
-      <c r="H189" s="9" t="inlineStr"/>
-      <c r="I189" s="9" t="inlineStr"/>
-      <c r="J189" s="9" t="inlineStr"/>
-      <c r="K189" s="9" t="inlineStr"/>
-      <c r="L189" s="9" t="inlineStr"/>
-      <c r="M189" s="9" t="inlineStr"/>
-      <c r="N189" s="9" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="F189" s="10" t="inlineStr"/>
+      <c r="G189" s="10" t="inlineStr"/>
+      <c r="H189" s="10" t="inlineStr"/>
+      <c r="I189" s="10" t="inlineStr"/>
+      <c r="J189" s="10" t="inlineStr"/>
+      <c r="K189" s="10" t="inlineStr"/>
+      <c r="L189" s="10" t="inlineStr"/>
+      <c r="M189" s="10" t="inlineStr"/>
+      <c r="N189" s="10" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="10" t="n"/>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="A190" s="11" t="n"/>
+      <c r="B190" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C190" s="9" t="inlineStr"/>
-      <c r="D190" s="9" t="inlineStr"/>
-      <c r="E190" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" s="9" t="inlineStr"/>
-      <c r="G190" s="9" t="inlineStr"/>
-      <c r="H190" s="9" t="inlineStr"/>
-      <c r="I190" s="9" t="inlineStr"/>
-      <c r="J190" s="9" t="inlineStr"/>
-      <c r="K190" s="9" t="inlineStr"/>
-      <c r="L190" s="9" t="inlineStr"/>
-      <c r="M190" s="9" t="inlineStr"/>
-      <c r="N190" s="9" t="inlineStr"/>
+      <c r="C190" s="10" t="inlineStr"/>
+      <c r="D190" s="10" t="inlineStr"/>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>140 dias</t>
+        </is>
+      </c>
+      <c r="F190" s="10" t="inlineStr"/>
+      <c r="G190" s="10" t="inlineStr"/>
+      <c r="H190" s="10" t="inlineStr"/>
+      <c r="I190" s="10" t="inlineStr"/>
+      <c r="J190" s="10" t="inlineStr"/>
+      <c r="K190" s="10" t="inlineStr"/>
+      <c r="L190" s="10" t="inlineStr"/>
+      <c r="M190" s="10" t="inlineStr"/>
+      <c r="N190" s="10" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>RAMOS DE PURPURA 06/23  |  Cód: 13.46.0147  |  Linha: LENÇOS  |  Subgrupo: CETIM DE POLIESTER  |  Grade: 90X90  |  Coleção: O9  |  U9</t>
+          <t>RAMOS DE PURPURA PINK PURPLE 06/23  |  Cód: 45.14.0058  |  Linha: LENÇOS  |  Subgrupo: MOUSSELINE DE POLIESTER  |  Grade: 45X210  |  Coleção: O9  |  47</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -6529,40 +6571,40 @@
         </is>
       </c>
       <c r="C192" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E192" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H192" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J192" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K192" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M192" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N192" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
@@ -6575,34 +6617,34 @@
       <c r="C193" s="5" t="inlineStr"/>
       <c r="D193" s="5" t="inlineStr"/>
       <c r="E193" s="6" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="F193" s="5" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="H193" s="5" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="J193" s="5" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K193" s="5" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M193" s="5" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -6614,126 +6656,120 @@
       </c>
       <c r="C194" s="5" t="inlineStr"/>
       <c r="D194" s="5" t="inlineStr"/>
-      <c r="E194" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>112 dias</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>91 dias</t>
+        </is>
+      </c>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t>61 dias</t>
+        </is>
+      </c>
+      <c r="H194" s="8" t="inlineStr">
+        <is>
+          <t>30 dias</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="inlineStr"/>
+      <c r="J194" s="5" t="inlineStr"/>
+      <c r="K194" s="5" t="inlineStr"/>
+      <c r="L194" s="5" t="inlineStr"/>
+      <c r="M194" s="5" t="inlineStr"/>
+      <c r="N194" s="5" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B195" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" s="9" t="n">
-        <v>0</v>
+      <c r="C195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E195" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N195" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B196" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr"/>
-      <c r="D196" s="9" t="inlineStr"/>
+      <c r="C196" s="10" t="inlineStr"/>
+      <c r="D196" s="10" t="inlineStr"/>
       <c r="E196" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="F196" s="9" t="inlineStr"/>
-      <c r="G196" s="9" t="inlineStr"/>
-      <c r="H196" s="9" t="inlineStr"/>
-      <c r="I196" s="9" t="inlineStr"/>
-      <c r="J196" s="9" t="inlineStr"/>
-      <c r="K196" s="9" t="inlineStr"/>
-      <c r="L196" s="9" t="inlineStr"/>
-      <c r="M196" s="9" t="inlineStr"/>
-      <c r="N196" s="9" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F196" s="10" t="inlineStr"/>
+      <c r="G196" s="10" t="inlineStr"/>
+      <c r="H196" s="10" t="inlineStr"/>
+      <c r="I196" s="10" t="inlineStr"/>
+      <c r="J196" s="10" t="inlineStr"/>
+      <c r="K196" s="10" t="inlineStr"/>
+      <c r="L196" s="10" t="inlineStr"/>
+      <c r="M196" s="10" t="inlineStr"/>
+      <c r="N196" s="10" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="10" t="n"/>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="A197" s="11" t="n"/>
+      <c r="B197" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C197" s="9" t="inlineStr"/>
-      <c r="D197" s="9" t="inlineStr"/>
-      <c r="E197" s="6" t="inlineStr">
-        <is>
-          <t>660 dias</t>
-        </is>
-      </c>
-      <c r="F197" s="9" t="inlineStr"/>
-      <c r="G197" s="9" t="inlineStr"/>
-      <c r="H197" s="9" t="inlineStr"/>
-      <c r="I197" s="9" t="inlineStr"/>
-      <c r="J197" s="9" t="inlineStr"/>
-      <c r="K197" s="9" t="inlineStr"/>
-      <c r="L197" s="9" t="inlineStr"/>
-      <c r="M197" s="9" t="inlineStr"/>
-      <c r="N197" s="9" t="inlineStr"/>
+      <c r="C197" s="10" t="inlineStr"/>
+      <c r="D197" s="10" t="inlineStr"/>
+      <c r="E197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="10" t="inlineStr"/>
+      <c r="G197" s="10" t="inlineStr"/>
+      <c r="H197" s="10" t="inlineStr"/>
+      <c r="I197" s="10" t="inlineStr"/>
+      <c r="J197" s="10" t="inlineStr"/>
+      <c r="K197" s="10" t="inlineStr"/>
+      <c r="L197" s="10" t="inlineStr"/>
+      <c r="M197" s="10" t="inlineStr"/>
+      <c r="N197" s="10" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -6747,40 +6783,40 @@
         </is>
       </c>
       <c r="C199" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E199" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F199" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G199" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J199" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K199" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M199" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200">
@@ -6796,31 +6832,31 @@
         <v>94</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="H200" s="5" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="J200" s="5" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="K200" s="5" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="M200" s="5" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="N200" s="5" t="n">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201">
@@ -6832,126 +6868,146 @@
       </c>
       <c r="C201" s="5" t="inlineStr"/>
       <c r="D201" s="5" t="inlineStr"/>
-      <c r="E201" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M201" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" s="5" t="n">
-        <v>0</v>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>281 dias</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>260 dias</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>230 dias</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>199 dias</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="inlineStr">
+        <is>
+          <t>169 dias</t>
+        </is>
+      </c>
+      <c r="J201" s="5" t="inlineStr">
+        <is>
+          <t>138 dias</t>
+        </is>
+      </c>
+      <c r="K201" s="8" t="inlineStr">
+        <is>
+          <t>107 dias</t>
+        </is>
+      </c>
+      <c r="L201" s="8" t="inlineStr">
+        <is>
+          <t>77 dias</t>
+        </is>
+      </c>
+      <c r="M201" s="8" t="inlineStr">
+        <is>
+          <t>46 dias</t>
+        </is>
+      </c>
+      <c r="N201" s="8" t="inlineStr">
+        <is>
+          <t>16 dias</t>
+        </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B202" s="9" t="inlineStr">
         <is>
           <t>VENDA (REAL)</t>
         </is>
       </c>
-      <c r="C202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D202" s="9" t="n">
-        <v>0</v>
+      <c r="C202" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D202" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E202" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N202" s="9" t="n">
+      <c r="F202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
-      <c r="B203" s="8" t="inlineStr">
+      <c r="B203" s="9" t="inlineStr">
         <is>
           <t>ESTOQUE (REAL)</t>
         </is>
       </c>
-      <c r="C203" s="9" t="inlineStr"/>
-      <c r="D203" s="9" t="inlineStr"/>
+      <c r="C203" s="10" t="inlineStr"/>
+      <c r="D203" s="10" t="inlineStr"/>
       <c r="E203" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="F203" s="9" t="inlineStr"/>
-      <c r="G203" s="9" t="inlineStr"/>
-      <c r="H203" s="9" t="inlineStr"/>
-      <c r="I203" s="9" t="inlineStr"/>
-      <c r="J203" s="9" t="inlineStr"/>
-      <c r="K203" s="9" t="inlineStr"/>
-      <c r="L203" s="9" t="inlineStr"/>
-      <c r="M203" s="9" t="inlineStr"/>
-      <c r="N203" s="9" t="inlineStr"/>
+      <c r="F203" s="10" t="inlineStr"/>
+      <c r="G203" s="10" t="inlineStr"/>
+      <c r="H203" s="10" t="inlineStr"/>
+      <c r="I203" s="10" t="inlineStr"/>
+      <c r="J203" s="10" t="inlineStr"/>
+      <c r="K203" s="10" t="inlineStr"/>
+      <c r="L203" s="10" t="inlineStr"/>
+      <c r="M203" s="10" t="inlineStr"/>
+      <c r="N203" s="10" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="10" t="n"/>
-      <c r="B204" s="8" t="inlineStr">
+      <c r="A204" s="11" t="n"/>
+      <c r="B204" s="9" t="inlineStr">
         <is>
           <t>DURACAO (REAL)</t>
         </is>
       </c>
-      <c r="C204" s="9" t="inlineStr"/>
-      <c r="D204" s="9" t="inlineStr"/>
+      <c r="C204" s="10" t="inlineStr"/>
+      <c r="D204" s="10" t="inlineStr"/>
       <c r="E204" s="6" t="inlineStr">
         <is>
           <t>313 dias</t>
         </is>
       </c>
-      <c r="F204" s="9" t="inlineStr"/>
-      <c r="G204" s="9" t="inlineStr"/>
-      <c r="H204" s="9" t="inlineStr"/>
-      <c r="I204" s="9" t="inlineStr"/>
-      <c r="J204" s="9" t="inlineStr"/>
-      <c r="K204" s="9" t="inlineStr"/>
-      <c r="L204" s="9" t="inlineStr"/>
-      <c r="M204" s="9" t="inlineStr"/>
-      <c r="N204" s="9" t="inlineStr"/>
+      <c r="F204" s="10" t="inlineStr"/>
+      <c r="G204" s="10" t="inlineStr"/>
+      <c r="H204" s="10" t="inlineStr"/>
+      <c r="I204" s="10" t="inlineStr"/>
+      <c r="J204" s="10" t="inlineStr"/>
+      <c r="K204" s="10" t="inlineStr"/>
+      <c r="L204" s="10" t="inlineStr"/>
+      <c r="M204" s="10" t="inlineStr"/>
+      <c r="N204" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -7173,7 +7229,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Relatório gerado em: 10/03/2026 16:08</t>
+          <t>Relatório gerado em: 10/03/2026 16:37</t>
         </is>
       </c>
     </row>

--- a/projecao_produtos_2026-03-10.xlsx
+++ b/projecao_produtos_2026-03-10.xlsx
@@ -577,7 +577,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Projeção de Estoque por Produto — Gerado em 10/03/2026 16:37</t>
+          <t>Projeção de Estoque por Produto — Gerado em 10/03/2026 17:18</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Relatório gerado em: 10/03/2026 16:37</t>
+          <t>Relatório gerado em: 10/03/2026 17:18</t>
         </is>
       </c>
     </row>
